--- a/data/trans_orig/IP07_A12_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07_A12_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de estar demasiado cansado/a para disfrutar de las cosas que le gustan, percibida por el adulto en 2023 (tasa de respuesta: 99,9%)</t>
+          <t>Menores según la frecuencia de estar demasiado cansado/a para disfrutar de las cosas que le gustan, percibida por el/la adulto/a en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1441</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4687</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4890</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>18,96%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5170</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1441</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5707</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>962</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>340</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3347</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>27,62%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1177</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3987</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,44%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7574</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9428</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2101</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6348</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,68%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6707</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2372</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14574</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>23,47%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>50,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>11893</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20403</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16016</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23833</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>76,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>18867</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11871</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>23569</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>66,01%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>41,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>82,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20939</t>
+          <t>18479</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15844</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>21920</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>39805</t>
+          <t>38880</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31511</t>
+          <t>32285</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46057</t>
+          <t>43970</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>83,59%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>26813</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>26813</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>26813</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28582</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28582</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>28582</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27535</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27535</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27535</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>56116</t>
+          <t>52605</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>56116</t>
+          <t>52605</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>56116</t>
+          <t>52605</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7644</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3812</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15594</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9036</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4520</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16159</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>16834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>17223</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10590</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26347</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8057</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6937</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3059</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13573</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>14670</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11314</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5830</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19269</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>11424</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6154</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19458</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37145</t>
+          <t>18731</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>27381</t>
+          <t>23289</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>15726</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48665</t>
+          <t>34225</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>62952</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>48929</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>80505</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,24%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>41523</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>27787</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>54198</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,7%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,86%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>64791</t>
+          <t>43033</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48815</t>
+          <t>33436</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83387</t>
+          <t>54307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>106313</t>
+          <t>105985</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84957</t>
+          <t>88534</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130019</t>
+          <t>127495</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>210939</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>192763</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>227443</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>71,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>65,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>76,74%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>190869</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>175459</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>214317</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73,47%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>217720</t>
+          <t>173375</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>195287</t>
+          <t>159690</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>235446</t>
+          <t>185356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>408590</t>
+          <t>384314</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>383522</t>
+          <t>362273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>438276</t>
+          <t>404833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>74,72%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>296398</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>296398</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>296398</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>327</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>259789</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>259789</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>259789</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>309246</t>
+          <t>245413</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>309246</t>
+          <t>245413</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>309246</t>
+          <t>245413</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>569035</t>
+          <t>541811</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>569035</t>
+          <t>541811</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>569035</t>
+          <t>541811</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3626</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9144</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1825</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8813</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14508</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -2197,107 +2197,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1509</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1492</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1509</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>5076</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>5431</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1492</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>5397</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8977</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>16462</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9,28%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>17,01%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>5725</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2431</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10451</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,94%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16384</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>14975</t>
+          <t>14797</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23364</t>
+          <t>22887</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>11812</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6985</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>18651</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12,21%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>19,27%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>9826</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>5600</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>15635</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>19,35%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12010</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6934</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>16383</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14664</t>
+          <t>15116</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30557</t>
+          <t>31318</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>70849</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>62088</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>78624</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>73,21%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>64,16%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>81,25%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>60730</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>53530</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>66709</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>75,18%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>66,26%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>82,58%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>76730</t>
+          <t>63327</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67496</t>
+          <t>55122</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84709</t>
+          <t>69488</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>137460</t>
+          <t>134177</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124878</t>
+          <t>122987</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146546</t>
+          <t>143997</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,55%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>96773</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>96773</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>96773</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>80781</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>80781</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>80781</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>102943</t>
+          <t>84248</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>102943</t>
+          <t>84248</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>102943</t>
+          <t>84248</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>183724</t>
+          <t>181021</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>183724</t>
+          <t>181021</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>183724</t>
+          <t>181021</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11270</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5845</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>19657</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>14977</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>9075</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>23044</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>6,24%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>15748</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>27018</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17479</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35125</t>
+          <t>37634</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>6021</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2555</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>11959</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>7328</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>3486</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>13845</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>7790</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2430</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>13811</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>22530</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>23637</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>15174</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>33778</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>18326</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>11385</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>26668</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28416</t>
+          <t>19065</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49434</t>
+          <t>27356</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>46742</t>
+          <t>42702</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34783</t>
+          <t>32389</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>68958</t>
+          <t>57482</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>76865</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>61815</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>97418</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>18,3%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>14,72%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>58055</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>43418</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>72831</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>11,76%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>19,73%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>79250</t>
+          <t>57670</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>63174</t>
+          <t>46454</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101345</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>137305</t>
+          <t>134535</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>115800</t>
+          <t>114712</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>163058</t>
+          <t>156284</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>302191</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>278960</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>319865</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>71,95%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>66,42%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>76,16%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>270465</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>253007</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>295159</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>73,27%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>68,54%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>315390</t>
+          <t>255180</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>289031</t>
+          <t>240268</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>336001</t>
+          <t>269836</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>585855</t>
+          <t>557371</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>555292</t>
+          <t>533483</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>615138</t>
+          <t>581580</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>419984</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>369151</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>439724</t>
+          <t>355453</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>808876</t>
+          <t>775437</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
